--- a/Penetration_Test_Round_3.xlsx
+++ b/Penetration_Test_Round_3.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Config done + fix coded (awaiting live email round-trip). Owner enabled 'Confirm email' in Supabase Auth (verified live 2026-07-08: signup no longer returns a session; example.com now rejected as invalid). Code half shipped so the app works with confirmation on: new app/auth/confirm/route.ts establishes the SSR session cookie (PKCE code + token_hash flows) with an open-redirect guard on 'next'; signup shows a 'check your email' notice instead of dead-redirecting; adminSignup defers code redemption to a new signed-in redeemAdminCode action (redeem needs a session); middleware lets a confirmed non-admin reach /admin-access to redeem. Verified: tsc passes; /auth/confirm fails safe to /login?error=confirm on bad/missing/expired token; open-redirect guard 9/9 unit tests; auth pages 200. PENDING: owner E2E on live (sign up real email -&gt; notice -&gt; click link -&gt; lands logged in; admin confirm-&gt;sign in-&gt;redeem code). If the link doesn't establish a session, switch the email template to the token_hash form (route already supports it).</t>
         </is>
       </c>
     </row>

--- a/Penetration_Test_Round_3.xlsx
+++ b/Penetration_Test_Round_3.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed. supabase/phase34_admin_redeem_hardening.sql revokes EXECUTE from public/anon (authenticated only) and adds a per-user lockout (5 wrong codes -&gt; 15-min lock, tracked in admin_access_attempts, RLS-on/no-policies; correct code clears it). Lockout is commit-safe (only RAISEs when already locked, so the failure/lock bookkeeping isn't rolled back). VERIFIED LIVE 2026-07-08: anon redeem_admin_access now HTTP 401 'permission denied for function' (was 200/false, unlimited). Throttle logic reviewed + a verify script (verify_pt3_05.sh &lt;token&gt;) exercises it (attempts 1-5 false/200, 6+ 'Too many attempts'/400); live throttle run pending a confirmed non-admin token (email confirmation from PT3-02 blocks minting one here). Happy path unchanged: a correct code on first try still elevates (never touches the throttle).</t>
         </is>
       </c>
     </row>
